--- a/Heiss_etal_2004/Evo_M1_Heiss_hominin_brain_expansion_dataset.xlsx
+++ b/Heiss_etal_2004/Evo_M1_Heiss_hominin_brain_expansion_dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/Heiss_etal_2004/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_8BE9F8DFB28352A174DDD56BBEB5463D2C1A0B10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{962E1E6B-7C10-0B43-B37A-A3630177C347}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_8BE9F8DFB28352A174DDD56BBEB5463D2C1A0B10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A22B84D4-9D73-BF4C-85B8-1E61564A895F}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="-7240" windowWidth="51200" windowHeight="28200" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34560" yWindow="-7240" windowWidth="51200" windowHeight="26640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -1413,7 +1413,7 @@
     <col min="2" max="2" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15">
+    <row r="1" spans="1:2" ht="16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30">
+    <row r="2" spans="1:2" ht="31">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30">
+    <row r="3" spans="1:2" ht="31">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30">
+    <row r="4" spans="1:2" ht="31">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15">
+    <row r="5" spans="1:2" ht="16">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30">
+    <row r="6" spans="1:2" ht="31">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15">
+    <row r="7" spans="1:2" ht="16">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15">
+    <row r="10" spans="1:2" ht="16">
       <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
@@ -1543,7 +1543,7 @@
     <col min="20" max="22" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="75">
+    <row r="1" spans="1:22" ht="80">
       <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
@@ -3125,7 +3125,7 @@
     <col min="1" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="45">
+    <row r="1" spans="1:22" ht="48">
       <c r="A1" s="3" t="s">
         <v>204</v>
       </c>
@@ -3860,7 +3860,7 @@
     <col min="4" max="4" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15">
+    <row r="1" spans="1:22" ht="16">
       <c r="A1" s="3" t="s">
         <v>275</v>
       </c>
@@ -3930,7 +3930,7 @@
       <c r="C4" t="s">
         <v>289</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
         <v>290</v>
       </c>
     </row>
@@ -4021,10 +4021,12 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D6" r:id="rId1" xr:uid="{3575B419-4B6B-1140-A0BD-C7284F6CEDBE}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{C5F9520D-239B-1643-A5B0-40912E7E406A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4039,7 +4041,7 @@
     <col min="5" max="5" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="30">
+    <row r="1" spans="1:22" ht="32">
       <c r="A1" s="3" t="s">
         <v>315</v>
       </c>
@@ -4329,6 +4331,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -4583,17 +4596,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DAA61FF-587F-42C3-A9E0-19D4FF6FB426}">
   <ds:schemaRefs>
@@ -4603,6 +4605,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA641F89-2642-4774-8E17-D6E5850AC44F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{397D44B4-1A5E-4074-8699-B926AEEEE665}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4619,21 +4638,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA641F89-2642-4774-8E17-D6E5850AC44F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>